--- a/data/trans_orig/P25D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>26164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480589</t>
+          <t>478091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500727</t>
+          <t>500362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439191</t>
+          <t>438812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>445472</t>
+          <t>445387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>922596</t>
+          <t>922776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>944826</t>
+          <t>944690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435462</t>
+          <t>435320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447510</t>
+          <t>448105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373139</t>
+          <t>372676</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380597</t>
+          <t>380628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812011</t>
+          <t>813143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826825</t>
+          <t>826695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657023</t>
+          <t>657189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667713</t>
+          <t>668264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157041</t>
+          <t>155592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165174</t>
+          <t>165045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>817875</t>
+          <t>818269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>832248</t>
+          <t>832676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,77 +1774,77 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6266</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12618</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>14959</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8062</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>25249</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6266</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13194</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>14959</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>7917</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>25308</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1014628</t>
+          <t>1014283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1027588</t>
+          <t>1026988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,82 +1887,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>969165</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>962813</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>973497</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1992222</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1981932</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1999119</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>969165</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>962237</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>973096</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1992222</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1981873</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1999264</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462288</t>
+          <t>462004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471971</t>
+          <t>471990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>834855</t>
+          <t>834950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>839544</t>
+          <t>839573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1300680</t>
+          <t>1299233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1310923</t>
+          <t>1310813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230870</t>
+          <t>231346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>745062</t>
+          <t>745039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>759986</t>
+          <t>759998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981139</t>
+          <t>982453</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>998377</t>
+          <t>998458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>52272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,39 +2803,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>23740</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>15198</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>35491</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>23740</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>36636</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>42754</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78645</t>
+          <t>79733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3312086</t>
+          <t>3314435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3344499</t>
+          <t>3343901</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,42 +2916,42 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3547370</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3535619</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3555912</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5203</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3547370</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3534474</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3555701</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6859172</t>
+          <t>6858084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6895427</t>
+          <t>6895063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26164</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>494643</t>
+          <t>540513</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478091</t>
+          <t>526257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500362</t>
+          <t>546469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>443410</t>
+          <t>484242</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438812</t>
+          <t>479838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>445387</t>
+          <t>486453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>938053</t>
+          <t>1024754</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>922776</t>
+          <t>1010985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>944690</t>
+          <t>1030795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504255</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504255</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504255</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950862</t>
+          <t>1037195</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950862</t>
+          <t>1037195</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950862</t>
+          <t>1037195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>443485</t>
+          <t>473109</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435320</t>
+          <t>465764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448105</t>
+          <t>478272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>378184</t>
+          <t>417788</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372676</t>
+          <t>412466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380628</t>
+          <t>420854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>821670</t>
+          <t>890898</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813143</t>
+          <t>881807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826695</t>
+          <t>896946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>481012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>481012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>481012</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381929</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381929</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381929</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>831995</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>831995</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>831995</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>664161</t>
+          <t>467365</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657189</t>
+          <t>461642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>470480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>162631</t>
+          <t>182895</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155592</t>
+          <t>176258</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165045</t>
+          <t>185465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>826791</t>
+          <t>650259</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>818269</t>
+          <t>642333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>832676</t>
+          <t>654602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166319</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166319</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166319</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834582</t>
+          <t>658440</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834582</t>
+          <t>658440</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834582</t>
+          <t>658440</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1023058</t>
+          <t>1115972</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1014283</t>
+          <t>1099622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026988</t>
+          <t>1122529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>969165</t>
+          <t>851805</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962813</t>
+          <t>845123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>973497</t>
+          <t>855091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1992222</t>
+          <t>1967775</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1981932</t>
+          <t>1955350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1999119</t>
+          <t>1977045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1128635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1128635</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1128635</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975431</t>
+          <t>858373</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975431</t>
+          <t>858373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975431</t>
+          <t>858373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2007181</t>
+          <t>1987007</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2007181</t>
+          <t>1987007</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2007181</t>
+          <t>1987007</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>469057</t>
+          <t>561792</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462004</t>
+          <t>553366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471990</t>
+          <t>564832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>838214</t>
+          <t>826887</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>834950</t>
+          <t>822841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>839573</t>
+          <t>828749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1307272</t>
+          <t>1388679</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1299233</t>
+          <t>1380127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1310813</t>
+          <t>1392359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472940</t>
+          <t>565784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472940</t>
+          <t>565784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472940</t>
+          <t>565784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840096</t>
+          <t>829473</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840096</t>
+          <t>829473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840096</t>
+          <t>829473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313036</t>
+          <t>1395257</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313036</t>
+          <t>1395257</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313036</t>
+          <t>1395257</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237775</t>
+          <t>234286</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231346</t>
+          <t>227856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>755766</t>
+          <t>838652</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>745039</t>
+          <t>828477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>759998</t>
+          <t>842776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>993541</t>
+          <t>1072937</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>982453</t>
+          <t>1061997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>998458</t>
+          <t>1077447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000160</t>
+          <t>1079720</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000160</t>
+          <t>1079720</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000160</t>
+          <t>1079720</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>26761</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>56442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>37763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42754</t>
+          <t>49361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79733</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3332179</t>
+          <t>3393035</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3314435</t>
+          <t>3376412</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3343901</t>
+          <t>3406093</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3547370</t>
+          <t>3602267</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3535619</t>
+          <t>3590448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3555912</t>
+          <t>3610714</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6879549</t>
+          <t>6995303</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6858084</t>
+          <t>6973815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6895063</t>
+          <t>7011705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3366707</t>
+          <t>3432854</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3366707</t>
+          <t>3432854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3366707</t>
+          <t>3432854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571110</t>
+          <t>3628211</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571110</t>
+          <t>3628211</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571110</t>
+          <t>3628211</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6937817</t>
+          <t>7061066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6937817</t>
+          <t>7061066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6937817</t>
+          <t>7061066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
